--- a/cronograma/Mayo_Julio_2026/Algoritmica_Prog_T2_Mes2_Junio.xlsx
+++ b/cronograma/Mayo_Julio_2026/Algoritmica_Prog_T2_Mes2_Junio.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="72">
   <si>
     <t>Construcción Civil</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Nombre del Profesor:</t>
+  </si>
+  <si>
+    <t>Enyerber Franco</t>
   </si>
   <si>
     <r>
@@ -56,67 +59,49 @@
     </r>
   </si>
   <si>
+    <t>23781625</t>
+  </si>
+  <si>
     <t>Dedicación: TIEMPO COMPLETO</t>
   </si>
   <si>
+    <t>TIEMPO COMPLETO</t>
+  </si>
+  <si>
     <t>Electricidad</t>
   </si>
   <si>
     <t>Carrera:</t>
   </si>
   <si>
+    <t>PNF Informática</t>
+  </si>
+  <si>
     <t>PNF:</t>
   </si>
   <si>
+    <t>PNFI</t>
+  </si>
+  <si>
+    <t>Mantenimiento Equipos Mecánicos</t>
+  </si>
+  <si>
     <t>Administración</t>
   </si>
   <si>
-    <t>Mantenimiento Equipos Mecánicos</t>
-  </si>
-  <si>
     <t>Semestre:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Desde:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> _________                 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <family val="2"/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>Hasta:</t>
-    </r>
-    <r>
-      <rPr>
-        <family val="2"/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> ________</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Trayecto:  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trimestre: </t>
+    <t>2026-2</t>
+  </si>
+  <si>
+    <t>Desde: 04/05/2026   Hasta: 25/07/2026</t>
+  </si>
+  <si>
+    <t>Trayecto:  I</t>
+  </si>
+  <si>
+    <t>Trimestre: II</t>
   </si>
   <si>
     <t xml:space="preserve">Desde: </t>
@@ -137,6 +122,9 @@
     <t xml:space="preserve">Unidad Curricular/Sección: </t>
   </si>
   <si>
+    <t>Algoritmica Y programacion I</t>
+  </si>
+  <si>
     <t>Mantenimiento Industrial</t>
   </si>
   <si>
@@ -150,6 +138,9 @@
   </si>
   <si>
     <t xml:space="preserve">                     Aula: </t>
+  </si>
+  <si>
+    <t>Laboratorio 1</t>
   </si>
   <si>
     <t>Banca y Finanzas</t>
@@ -1277,16 +1268,22 @@
         <v>5</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
+      <c r="D7" s="8" t="s">
+        <v>6</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="10"/>
+        <v>7</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="H7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="11"/>
+        <v>9</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>10</v>
+      </c>
       <c r="J7" s="11"/>
       <c r="K7" s="11"/>
       <c r="M7" s="5"/>
@@ -1294,22 +1291,24 @@
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="15"/>
+        <v>12</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>13</v>
+      </c>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="18"/>
@@ -1317,94 +1316,100 @@
       <c r="K8" s="6"/>
       <c r="M8" s="5"/>
       <c r="P8" s="12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q8" s="13" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="D9" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E9" s="19"/>
       <c r="F9" s="20" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="M9" s="5"/>
       <c r="P9" s="12" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="22"/>
       <c r="E10" s="23"/>
       <c r="F10" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="25"/>
+        <v>28</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>29</v>
+      </c>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
       <c r="K10" s="26"/>
       <c r="M10" s="5"/>
       <c r="P10" s="12" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="27" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
       <c r="E11" s="29" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G11" s="28"/>
       <c r="H11" s="28"/>
       <c r="I11" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="31"/>
+        <v>34</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>35</v>
+      </c>
       <c r="K11" s="31"/>
       <c r="M11" s="5"/>
       <c r="P11" s="12" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1421,7 +1426,7 @@
       <c r="K12" s="35"/>
       <c r="M12" s="5"/>
       <c r="P12" s="37" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q12" s="13" t="s">
         <v>0</v>
@@ -1429,14 +1434,14 @@
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
       <c r="D13" s="39"/>
       <c r="E13" s="40"/>
       <c r="F13" s="41" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G13" s="41"/>
       <c r="H13" s="41"/>
@@ -1445,61 +1450,61 @@
       <c r="K13" s="42"/>
       <c r="M13" s="5"/>
       <c r="P13" s="37" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="Q13" s="43"/>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D14" s="47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E14" s="48" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F14" s="49" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G14" s="50" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H14" s="50" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I14" s="51" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="J14" s="52" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K14" s="53" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="M14" s="5"/>
       <c r="P14" s="37" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" ht="51.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="54" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B15" s="55" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C15" s="56" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D15" s="57" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E15" s="58">
         <v>4</v>
@@ -1513,47 +1518,47 @@
     </row>
     <row r="16" ht="51.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="60" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B16" s="55" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C16" s="56" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E16" s="58">
         <v>4</v>
       </c>
       <c r="F16" s="55" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G16" s="59"/>
       <c r="H16" s="59" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="I16" s="56" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J16" s="50" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K16" s="58"/>
     </row>
     <row r="17" ht="64.5" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="60" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B17" s="55" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E17" s="58">
         <v>4</v>
@@ -1565,41 +1570,41 @@
       <c r="J17" s="50"/>
       <c r="K17" s="58"/>
       <c r="P17" s="12" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" ht="64.5" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="60" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C18" s="56" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E18" s="58">
         <v>4</v>
       </c>
       <c r="F18" s="55" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G18" s="59"/>
       <c r="H18" s="59" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I18" s="56" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J18" s="50" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K18" s="58"/>
       <c r="P18" s="12" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" ht="33" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1631,7 +1636,7 @@
       <c r="D21" s="69"/>
       <c r="E21" s="69"/>
       <c r="F21" s="69" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G21" s="69"/>
       <c r="H21" s="69"/>
